--- a/result/XRCC3_LUAD_Tables.xlsx
+++ b/result/XRCC3_LUAD_Tables.xlsx
@@ -882,27 +882,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
     </row>
@@ -929,27 +929,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>-0.089</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>0.061</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>-0.055</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.026</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.081</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.089</t>
         </is>
       </c>
     </row>
@@ -968,27 +968,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.265</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.317</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.641</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.138</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.104</t>
         </is>
       </c>
     </row>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0.074</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>-0.016</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.074</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1054,34 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>0.181</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.774</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.181</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>-0.089</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1106,22 +1106,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.069</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.055</t>
         </is>
       </c>
     </row>
@@ -1134,40 +1134,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.468</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.317</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1177,37 +1177,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>-0.063</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.062</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.065</t>
         </is>
       </c>
     </row>
@@ -1220,40 +1220,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.468</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.239</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1263,37 +1263,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>-0.063</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.062</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>0.037</t>
         </is>
       </c>
     </row>
@@ -1306,40 +1306,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.257</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.504</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>ALKExpression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1349,37 +1349,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.069</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>0.062</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.005</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.055</t>
         </is>
       </c>
     </row>
@@ -1392,40 +1392,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.641</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.257</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.928</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>BRAFExpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1435,32 +1435,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.089</t>
+          <t>0.081</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.065</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1478,32 +1478,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.239</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.504</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.928</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,11 +1546,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.014</v>
+        <v>1.013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.209</t>
         </is>
       </c>
     </row>
@@ -1565,82 +1565,142 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.739</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XRCC3group_Low</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.627</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.065</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.189</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>0.916</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pathologic_stage_2.0</t>
+          <t>ALKExpression</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.117</v>
+        <v>0.993</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.198</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pathologic_stage_3.0</t>
+          <t>BRAFExpression</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.784</v>
+        <v>0.998</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.150</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>XRCC3group_Low</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.342</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pathologic_stage_2.0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>pathologic_stage_4.0</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2.553</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.009</t>
+      <c r="B12" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.018</t>
         </is>
       </c>
     </row>

--- a/result/XRCC3_LUAD_Tables.xlsx
+++ b/result/XRCC3_LUAD_Tables.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.125</t>
         </is>
       </c>
     </row>
@@ -508,342 +509,328 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">  FEMALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.038</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FEMALE</t>
+          <t xml:space="preserve">  MALE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MALE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>123</v>
-      </c>
-      <c r="C8" t="n">
-        <v>101</v>
-      </c>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>131</v>
+      </c>
+      <c r="C9" t="n">
+        <v>131</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.089</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>131</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.089</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>18</v>
-      </c>
-      <c r="C13" t="n">
-        <v>6</v>
-      </c>
+          <t>pathologic_M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pathologic_M</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>159</v>
+      </c>
+      <c r="C14" t="n">
+        <v>163</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>163</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.027</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>18</v>
-      </c>
-      <c r="C16" t="n">
-        <v>6</v>
-      </c>
+          <t>pathologic_N</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pathologic_N</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>164</v>
+      </c>
+      <c r="C17" t="n">
+        <v>152</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.282</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>152</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.282</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
+          <t>pathologic_T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pathologic_T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>80</v>
+      </c>
+      <c r="C22" t="n">
+        <v>84</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.592</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="C23" t="n">
-        <v>84</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.592</t>
-        </is>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>7</v>
-      </c>
-      <c r="C26" t="n">
-        <v>11</v>
-      </c>
+          <t>SmokingStatus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SmokingStatus</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>68</v>
+      </c>
+      <c r="C27" t="n">
+        <v>91</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.027</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>68</v>
+        <v>178</v>
       </c>
       <c r="C28" t="n">
-        <v>91</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.034</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>178</v>
-      </c>
-      <c r="C29" t="n">
         <v>155</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -856,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +892,11 @@
           <t>BRAFExpression</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EGFR_Mut_Binary</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -929,27 +921,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.089</t>
+          <t>-0.103</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.073</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-0.005</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.060</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.074</t>
         </is>
       </c>
     </row>
@@ -957,7 +954,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -968,27 +965,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>0.905</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.185</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.281</t>
         </is>
       </c>
     </row>
@@ -1036,6 +1038,11 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>-0.016</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1050,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1077,6 +1084,11 @@
           <t>0.774</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.611</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1091,7 +1103,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.089</t>
+          <t>-0.103</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1106,22 +1118,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1146,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1145,22 +1162,27 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.265</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.865</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1187,7 +1209,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1197,17 +1219,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.057</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.102</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1242,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1230,23 +1257,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.078</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.139</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1295,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.073</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1273,12 +1305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.057</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1288,12 +1320,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.008</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1338,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1316,23 +1353,28 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.940</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.904</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1391,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-0.005</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1359,17 +1401,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1379,7 +1421,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1434,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>0.905</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1402,23 +1449,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.372</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.469</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1487,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1445,27 +1497,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1530,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.185</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1488,25 +1545,126 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.122</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EGFR_Mut_Binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-0.074</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-0.102</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.107</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.281</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.611</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.865</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.469</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.122</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2646,4 +2804,99 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cancer Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chi-square</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LUAD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>XRCC3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.473</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.062</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LUAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>XRCC3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.657</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.418</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/result/XRCC3_LUAD_Tables.xlsx
+++ b/result/XRCC3_LUAD_Tables.xlsx
@@ -1677,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,6 +1693,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>P-value</t>
         </is>
       </c>
@@ -1706,7 +1716,13 @@
       <c r="B2" t="n">
         <v>1.013</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>0.209</t>
         </is>
@@ -1721,7 +1737,13 @@
       <c r="B3" t="n">
         <v>0.999</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.739</t>
         </is>
@@ -1736,7 +1758,13 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.065</t>
         </is>
@@ -1751,7 +1779,13 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>0.916</t>
         </is>
@@ -1766,7 +1800,13 @@
       <c r="B6" t="n">
         <v>0.993</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.198</t>
         </is>
@@ -1781,7 +1821,13 @@
       <c r="B7" t="n">
         <v>0.998</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>0.150</t>
         </is>
@@ -1796,7 +1842,13 @@
       <c r="B8" t="n">
         <v>0.605</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.012</t>
         </is>
@@ -1811,7 +1863,13 @@
       <c r="B9" t="n">
         <v>1.212</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>0.342</t>
         </is>
@@ -1826,7 +1884,13 @@
       <c r="B10" t="n">
         <v>2.135</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>0.001</t>
         </is>
@@ -1841,7 +1905,13 @@
       <c r="B11" t="n">
         <v>2.859</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="n">
+        <v>1.779</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.597</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1856,7 +1926,13 @@
       <c r="B12" t="n">
         <v>2.354</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.796</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>0.018</t>
         </is>
@@ -1936,7 +2012,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -2171,7 +2247,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -2406,7 +2482,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2641,7 +2717,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>

--- a/result/XRCC3_LUAD_Tables.xlsx
+++ b/result/XRCC3_LUAD_Tables.xlsx
@@ -10,8 +10,7 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1949,945 +1948,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Coefficient</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Lower</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>P-value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0350</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7.1984e-02</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>409.3715</v>
-      </c>
-      <c r="C8" t="n">
-        <v>269.411</v>
-      </c>
-      <c r="D8" t="n">
-        <v>549.3321</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6.7775</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-35.8426</v>
-      </c>
-      <c r="D9" t="n">
-        <v>49.3976</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.755</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-1.5578</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-52.7712</v>
-      </c>
-      <c r="D10" t="n">
-        <v>49.6556</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.952</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.2108</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-56.8703</v>
-      </c>
-      <c r="D11" t="n">
-        <v>57.2919</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.994</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>39.9474</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-55.2119</v>
-      </c>
-      <c r="D12" t="n">
-        <v>135.1067</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.409</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-1.8352</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-3.9031</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.2326</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.082</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.048</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.2765</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.8196</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.008</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0515</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>8.0929e-03</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>406.4946</v>
-      </c>
-      <c r="C22" t="n">
-        <v>267.9957</v>
-      </c>
-      <c r="D22" t="n">
-        <v>544.9935</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1.9377</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-40.523</v>
-      </c>
-      <c r="D23" t="n">
-        <v>44.3985</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.929</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>31.8701</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-13.4147</v>
-      </c>
-      <c r="D24" t="n">
-        <v>77.1549</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-14.3775</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-90.7573</v>
-      </c>
-      <c r="D25" t="n">
-        <v>62.0022</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.711</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>-85.7345</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-193.7031</v>
-      </c>
-      <c r="D26" t="n">
-        <v>22.234</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.119</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>-1.9792</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-3.9999</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.0415</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.055</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1.134</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.3733</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.8947</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.004</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.0410</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3.5423e-02</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>396.297</v>
-      </c>
-      <c r="C36" t="n">
-        <v>256.8791</v>
-      </c>
-      <c r="D36" t="n">
-        <v>535.7148999999999</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>10.5203</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-32.025</v>
-      </c>
-      <c r="D37" t="n">
-        <v>53.0657</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.627</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>-16.4483</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-70.1653</v>
-      </c>
-      <c r="D38" t="n">
-        <v>37.2687</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.547</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.6071</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-59.4938</v>
-      </c>
-      <c r="D39" t="n">
-        <v>60.708</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.984</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>233.0582</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-32.2156</v>
-      </c>
-      <c r="D40" t="n">
-        <v>498.3321</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.085</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>-1.5809</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-3.6565</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.4947</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.135</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1.0205</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.2475</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1.7935</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.010</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0146</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>4.9095e-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>322.5107</v>
-      </c>
-      <c r="C50" t="n">
-        <v>176.0425</v>
-      </c>
-      <c r="D50" t="n">
-        <v>468.9789</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>-0.9008</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-46.3087</v>
-      </c>
-      <c r="D51" t="n">
-        <v>44.5071</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.969</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>56.4384</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-29.8154</v>
-      </c>
-      <c r="D52" t="n">
-        <v>142.6922</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.199</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>-0.1854</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-2.3919</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.0211</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.869</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.5122</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.3236</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.348</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.229</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/XRCC3_LUAD_Tables.xlsx
+++ b/result/XRCC3_LUAD_Tables.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1948,6 +1949,966 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0335</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.5314e-02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>404.2769</v>
+      </c>
+      <c r="C8" t="n">
+        <v>259.7069</v>
+      </c>
+      <c r="D8" t="n">
+        <v>548.8469</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6.3325</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-35.7356</v>
+      </c>
+      <c r="D9" t="n">
+        <v>48.4006</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.767</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-1.8898</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-3.9429</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.071</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.8387</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5.472</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-16.9269</v>
+      </c>
+      <c r="D12" t="n">
+        <v>27.8709</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.0572</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7.8813e-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>379.8312</v>
+      </c>
+      <c r="C20" t="n">
+        <v>234.4197</v>
+      </c>
+      <c r="D20" t="n">
+        <v>525.2428</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-42.392</v>
+      </c>
+      <c r="D21" t="n">
+        <v>43.1328</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.986</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>26.3238</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-20.4063</v>
+      </c>
+      <c r="D22" t="n">
+        <v>73.0538</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.269</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-31.1965</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-112.0856</v>
+      </c>
+      <c r="D23" t="n">
+        <v>49.6926</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.449</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-117.6025</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-236.5873</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.3822</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.053</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-1.9149</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-3.955</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.066</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.1692</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.9327</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>16.1693</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-9.071</v>
+      </c>
+      <c r="D27" t="n">
+        <v>41.4096</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.208</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0.0429</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5.0231e-02</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>385.1541</v>
+      </c>
+      <c r="C35" t="n">
+        <v>236.1287</v>
+      </c>
+      <c r="D35" t="n">
+        <v>534.1796000000001</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>9.6531</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-33.1099</v>
+      </c>
+      <c r="D36" t="n">
+        <v>52.4162</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.657</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-26.1035</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-88.70529999999999</v>
+      </c>
+      <c r="D37" t="n">
+        <v>36.4984</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.413</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-16.7656</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-100.8467</v>
+      </c>
+      <c r="D38" t="n">
+        <v>67.3156</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.695</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>215.592</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-55.9509</v>
+      </c>
+      <c r="D39" t="n">
+        <v>487.1348</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-1.5947</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-3.6846</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0.134</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.0254</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.8012</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>9.6914</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-23.1689</v>
+      </c>
+      <c r="D42" t="n">
+        <v>42.5517</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0.562</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0.0151</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>6.2441e-01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>331.1695</v>
+      </c>
+      <c r="C50" t="n">
+        <v>176.6512</v>
+      </c>
+      <c r="D50" t="n">
+        <v>485.6878</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-1.1893</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-47.0801</v>
+      </c>
+      <c r="D51" t="n">
+        <v>44.7015</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.959</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>61.5523</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-48.305</v>
+      </c>
+      <c r="D52" t="n">
+        <v>171.4096</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.271</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.2563</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-2.4768</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.9641</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.820</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.3179</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.3654</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0.221</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-2.4592</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-31.5433</v>
+      </c>
+      <c r="D55" t="n">
+        <v>26.6249</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.868</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/XRCC3_LUAD_Tables.xlsx
+++ b/result/XRCC3_LUAD_Tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1677,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1714,17 +1715,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.013</v>
+        <v>1.014</v>
       </c>
       <c r="C2" t="n">
-        <v>0.993</v>
+        <v>0.995</v>
       </c>
       <c r="D2" t="n">
         <v>1.033</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.145</t>
         </is>
       </c>
     </row>
@@ -1738,203 +1739,119 @@
         <v>0.999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.991</v>
+        <v>0.992</v>
       </c>
       <c r="D3" t="n">
-        <v>1.006</v>
+        <v>1.007</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.857</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>XRCC3group_Low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.627</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.429</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.915</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.016</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>1.189</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>0.382</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>pathologic_stage_2.0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.993</v>
+        <v>2.117</v>
       </c>
       <c r="C6" t="n">
-        <v>0.982</v>
+        <v>1.336</v>
       </c>
       <c r="D6" t="n">
-        <v>1.004</v>
+        <v>3.353</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>pathologic_stage_3.0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.998</v>
+        <v>2.784</v>
       </c>
       <c r="C7" t="n">
-        <v>0.996</v>
+        <v>1.736</v>
       </c>
       <c r="D7" t="n">
-        <v>1.001</v>
+        <v>4.466</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.150</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XRCC3group_Low</t>
+          <t>pathologic_stage_4.0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.605</v>
+        <v>2.553</v>
       </c>
       <c r="C8" t="n">
-        <v>0.409</v>
+        <v>1.265</v>
       </c>
       <c r="D8" t="n">
-        <v>0.895</v>
+        <v>5.152</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.012</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>gender_MALE</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.212</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.342</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>pathologic_stage_2.0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.135</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.337</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pathologic_stage_3.0</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.859</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.779</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4.597</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.354</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.156</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.796</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.018</t>
+          <t>0.009</t>
         </is>
       </c>
     </row>
@@ -1949,18 +1866,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Clinical Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Hazard Ratio (HR)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1980,923 +1897,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>== [ Model: Base Model (No Stage) ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.135</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.785</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0335</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>XRCC3group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.5314e-02</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>404.2769</v>
-      </c>
-      <c r="C8" t="n">
-        <v>259.7069</v>
-      </c>
-      <c r="D8" t="n">
-        <v>548.8469</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6.3325</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-35.7356</v>
-      </c>
-      <c r="D9" t="n">
-        <v>48.4006</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.767</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-1.8898</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-3.9429</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1633</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.071</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.074</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.3093</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.8387</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5.472</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-16.9269</v>
-      </c>
-      <c r="D12" t="n">
-        <v>27.8709</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.631</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <f>== [ Model: Base + Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0.0572</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7.8813e-03</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>379.8312</v>
-      </c>
-      <c r="C20" t="n">
-        <v>234.4197</v>
-      </c>
-      <c r="D20" t="n">
-        <v>525.2428</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.3704</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-42.392</v>
-      </c>
-      <c r="D21" t="n">
-        <v>43.1328</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0.986</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>26.3238</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-20.4063</v>
-      </c>
-      <c r="D22" t="n">
-        <v>73.0538</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.269</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-31.1965</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-112.0856</v>
-      </c>
-      <c r="D23" t="n">
-        <v>49.6926</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.449</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>-117.6025</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-236.5873</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.3822</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.053</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-1.9149</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-3.955</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.1253</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.066</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1.1692</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.4058</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.9327</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>16.1693</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-9.071</v>
-      </c>
-      <c r="D27" t="n">
-        <v>41.4096</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.208</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <f>== [ Model: Base + Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>0.0429</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>5.0231e-02</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>385.1541</v>
-      </c>
-      <c r="C35" t="n">
-        <v>236.1287</v>
-      </c>
-      <c r="D35" t="n">
-        <v>534.1796000000001</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>9.6531</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-33.1099</v>
-      </c>
-      <c r="D36" t="n">
-        <v>52.4162</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.657</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>-26.1035</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-88.70529999999999</v>
-      </c>
-      <c r="D37" t="n">
-        <v>36.4984</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.413</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>-16.7656</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-100.8467</v>
-      </c>
-      <c r="D38" t="n">
-        <v>67.3156</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.695</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>215.592</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-55.9509</v>
-      </c>
-      <c r="D39" t="n">
-        <v>487.1348</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.119</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>-1.5947</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-3.6846</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.4952</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.134</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1.0254</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.2496</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.8012</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.010</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>9.6914</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-23.1689</v>
-      </c>
-      <c r="D42" t="n">
-        <v>42.5517</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.562</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>== [ Model: Base + Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>XRCC3expression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0151</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>6.2441e-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>331.1695</v>
-      </c>
-      <c r="C50" t="n">
-        <v>176.6512</v>
-      </c>
-      <c r="D50" t="n">
-        <v>485.6878</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>-1.1893</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-47.0801</v>
-      </c>
-      <c r="D51" t="n">
-        <v>44.7015</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.959</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>61.5523</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-48.305</v>
-      </c>
-      <c r="D52" t="n">
-        <v>171.4096</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.271</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>-0.2563</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-2.4768</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.9641</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.820</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.5237000000000001</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.3179</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.3654</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.221</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-2.4592</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-31.5433</v>
-      </c>
-      <c r="D55" t="n">
-        <v>26.6249</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0.868</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.325</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2909,6 +2012,1117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0325</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.2374e-02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>415.6087</v>
+      </c>
+      <c r="C8" t="n">
+        <v>280.5807</v>
+      </c>
+      <c r="D8" t="n">
+        <v>550.6367</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.2323</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-34.2742</v>
+      </c>
+      <c r="D9" t="n">
+        <v>48.7388</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.732</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-1.9199</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-3.9458</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.063</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.0564</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.8166</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0350</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7.1984e-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>409.3715</v>
+      </c>
+      <c r="C19" t="n">
+        <v>269.411</v>
+      </c>
+      <c r="D19" t="n">
+        <v>549.3321</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6.7775</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-35.8426</v>
+      </c>
+      <c r="D20" t="n">
+        <v>49.3976</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.755</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-1.5578</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-52.7712</v>
+      </c>
+      <c r="D21" t="n">
+        <v>49.6556</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.952</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.2108</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-56.8703</v>
+      </c>
+      <c r="D22" t="n">
+        <v>57.2919</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.994</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>39.9474</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-55.2119</v>
+      </c>
+      <c r="D23" t="n">
+        <v>135.1067</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.409</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-1.8352</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-3.9031</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.2326</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.082</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.8196</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0515</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8.0929e-03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>406.4946</v>
+      </c>
+      <c r="C33" t="n">
+        <v>267.9957</v>
+      </c>
+      <c r="D33" t="n">
+        <v>544.9935</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.9377</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-40.523</v>
+      </c>
+      <c r="D34" t="n">
+        <v>44.3985</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.929</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>31.8701</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-13.4147</v>
+      </c>
+      <c r="D35" t="n">
+        <v>77.1549</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.167</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-14.3775</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-90.7573</v>
+      </c>
+      <c r="D36" t="n">
+        <v>62.0022</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.711</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-85.7345</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-193.7031</v>
+      </c>
+      <c r="D37" t="n">
+        <v>22.234</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-1.9792</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-3.9999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.8947</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0410</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3.5423e-02</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>396.297</v>
+      </c>
+      <c r="C47" t="n">
+        <v>256.8791</v>
+      </c>
+      <c r="D47" t="n">
+        <v>535.7148999999999</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>10.5203</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-32.025</v>
+      </c>
+      <c r="D48" t="n">
+        <v>53.0657</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.627</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>-16.4483</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-70.1653</v>
+      </c>
+      <c r="D49" t="n">
+        <v>37.2687</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.547</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.6071</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-59.4938</v>
+      </c>
+      <c r="D50" t="n">
+        <v>60.708</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.984</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>233.0582</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-32.2156</v>
+      </c>
+      <c r="D51" t="n">
+        <v>498.3321</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.085</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-1.5809</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-3.6565</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.4947</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.135</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1.0205</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.7935</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>XRCC3expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>XRCC3expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0146</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4.9095e-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>322.5107</v>
+      </c>
+      <c r="C61" t="n">
+        <v>176.0425</v>
+      </c>
+      <c r="D61" t="n">
+        <v>468.9789</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>-0.9008</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-46.3087</v>
+      </c>
+      <c r="D62" t="n">
+        <v>44.5071</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.969</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>56.4384</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-29.8154</v>
+      </c>
+      <c r="D63" t="n">
+        <v>142.6922</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.199</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>-0.1854</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-2.3919</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2.0211</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.869</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.5122</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.3236</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0.229</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2957,12 +3171,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.473</t>
+          <t>3.277</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.070</t>
         </is>
       </c>
     </row>

--- a/result/XRCC3_LUAD_Tables.xlsx
+++ b/result/XRCC3_LUAD_Tables.xlsx
@@ -2012,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,15 +2028,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -2050,7 +2045,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2065,7 +2059,6 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2080,7 +2073,6 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2095,7 +2087,6 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2110,7 +2101,6 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2121,7 +2111,6 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2132,13 +2121,12 @@
       <c r="B8" t="n">
         <v>415.6087</v>
       </c>
-      <c r="C8" t="n">
-        <v>280.5807</v>
-      </c>
-      <c r="D8" t="n">
-        <v>550.6367</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>280.581-550.637</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2153,13 +2141,12 @@
       <c r="B9" t="n">
         <v>7.2323</v>
       </c>
-      <c r="C9" t="n">
-        <v>-34.2742</v>
-      </c>
-      <c r="D9" t="n">
-        <v>48.7388</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-34.274-48.739</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>0.732</t>
         </is>
@@ -2174,13 +2161,12 @@
       <c r="B10" t="n">
         <v>-1.9199</v>
       </c>
-      <c r="C10" t="n">
-        <v>-3.9458</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-3.946-0.106</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.063</t>
         </is>
@@ -2195,13 +2181,12 @@
       <c r="B11" t="n">
         <v>1.0564</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.2963</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.8166</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.296-1.817</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.007</t>
         </is>
@@ -2212,7 +2197,6 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13">
@@ -2222,7 +2206,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2237,7 +2220,6 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2252,7 +2234,6 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2267,7 +2248,6 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2282,7 +2262,6 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2293,7 +2272,6 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2304,13 +2282,12 @@
       <c r="B19" t="n">
         <v>409.3715</v>
       </c>
-      <c r="C19" t="n">
-        <v>269.411</v>
-      </c>
-      <c r="D19" t="n">
-        <v>549.3321</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>269.411-549.3321</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2325,13 +2302,12 @@
       <c r="B20" t="n">
         <v>6.7775</v>
       </c>
-      <c r="C20" t="n">
-        <v>-35.8426</v>
-      </c>
-      <c r="D20" t="n">
-        <v>49.3976</v>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-35.8426-49.3976</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>0.755</t>
         </is>
@@ -2346,13 +2322,12 @@
       <c r="B21" t="n">
         <v>-1.5578</v>
       </c>
-      <c r="C21" t="n">
-        <v>-52.7712</v>
-      </c>
-      <c r="D21" t="n">
-        <v>49.6556</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-52.7712-49.6556</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>0.952</t>
         </is>
@@ -2367,13 +2342,12 @@
       <c r="B22" t="n">
         <v>0.2108</v>
       </c>
-      <c r="C22" t="n">
-        <v>-56.8703</v>
-      </c>
-      <c r="D22" t="n">
-        <v>57.2919</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-56.8703-57.2919</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>0.994</t>
         </is>
@@ -2388,13 +2362,12 @@
       <c r="B23" t="n">
         <v>39.9474</v>
       </c>
-      <c r="C23" t="n">
-        <v>-55.2119</v>
-      </c>
-      <c r="D23" t="n">
-        <v>135.1067</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-55.2119-135.1067</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>0.409</t>
         </is>
@@ -2409,13 +2382,12 @@
       <c r="B24" t="n">
         <v>-1.8352</v>
       </c>
-      <c r="C24" t="n">
-        <v>-3.9031</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.2326</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-3.9031-0.2326</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>0.082</t>
         </is>
@@ -2430,13 +2402,12 @@
       <c r="B25" t="n">
         <v>1.048</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.2765</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.8196</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.2765-1.8196</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.008</t>
         </is>
@@ -2447,7 +2418,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27">
@@ -2457,7 +2427,6 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2472,7 +2441,6 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2487,7 +2455,6 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2502,7 +2469,6 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2517,7 +2483,6 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2528,7 +2493,6 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2539,13 +2503,12 @@
       <c r="B33" t="n">
         <v>406.4946</v>
       </c>
-      <c r="C33" t="n">
-        <v>267.9957</v>
-      </c>
-      <c r="D33" t="n">
-        <v>544.9935</v>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>267.9957-544.9935</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2560,13 +2523,12 @@
       <c r="B34" t="n">
         <v>1.9377</v>
       </c>
-      <c r="C34" t="n">
-        <v>-40.523</v>
-      </c>
-      <c r="D34" t="n">
-        <v>44.3985</v>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-40.523-44.3985</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>0.929</t>
         </is>
@@ -2581,13 +2543,12 @@
       <c r="B35" t="n">
         <v>31.8701</v>
       </c>
-      <c r="C35" t="n">
-        <v>-13.4147</v>
-      </c>
-      <c r="D35" t="n">
-        <v>77.1549</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-13.4147-77.1549</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>0.167</t>
         </is>
@@ -2602,13 +2563,12 @@
       <c r="B36" t="n">
         <v>-14.3775</v>
       </c>
-      <c r="C36" t="n">
-        <v>-90.7573</v>
-      </c>
-      <c r="D36" t="n">
-        <v>62.0022</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-90.7573-62.0022</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>0.711</t>
         </is>
@@ -2623,13 +2583,12 @@
       <c r="B37" t="n">
         <v>-85.7345</v>
       </c>
-      <c r="C37" t="n">
-        <v>-193.7031</v>
-      </c>
-      <c r="D37" t="n">
-        <v>22.234</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-193.7031-22.234</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>0.119</t>
         </is>
@@ -2644,13 +2603,12 @@
       <c r="B38" t="n">
         <v>-1.9792</v>
       </c>
-      <c r="C38" t="n">
-        <v>-3.9999</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0415</v>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-3.9999-0.0415</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>0.055</t>
         </is>
@@ -2665,13 +2623,12 @@
       <c r="B39" t="n">
         <v>1.134</v>
       </c>
-      <c r="C39" t="n">
-        <v>0.3733</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.8947</v>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0.3733-1.8947</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
@@ -2682,7 +2639,6 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41">
@@ -2692,7 +2648,6 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2707,7 +2662,6 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2722,7 +2676,6 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2737,7 +2690,6 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2752,7 +2704,6 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2763,7 +2714,6 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2774,13 +2724,12 @@
       <c r="B47" t="n">
         <v>396.297</v>
       </c>
-      <c r="C47" t="n">
-        <v>256.8791</v>
-      </c>
-      <c r="D47" t="n">
-        <v>535.7148999999999</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>256.8791-535.7149</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2795,13 +2744,12 @@
       <c r="B48" t="n">
         <v>10.5203</v>
       </c>
-      <c r="C48" t="n">
-        <v>-32.025</v>
-      </c>
-      <c r="D48" t="n">
-        <v>53.0657</v>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-32.025-53.0657</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>0.627</t>
         </is>
@@ -2816,13 +2764,12 @@
       <c r="B49" t="n">
         <v>-16.4483</v>
       </c>
-      <c r="C49" t="n">
-        <v>-70.1653</v>
-      </c>
-      <c r="D49" t="n">
-        <v>37.2687</v>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-70.1653-37.2687</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>0.547</t>
         </is>
@@ -2837,13 +2784,12 @@
       <c r="B50" t="n">
         <v>0.6071</v>
       </c>
-      <c r="C50" t="n">
-        <v>-59.4938</v>
-      </c>
-      <c r="D50" t="n">
-        <v>60.708</v>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-59.4938-60.708</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>0.984</t>
         </is>
@@ -2858,13 +2804,12 @@
       <c r="B51" t="n">
         <v>233.0582</v>
       </c>
-      <c r="C51" t="n">
-        <v>-32.2156</v>
-      </c>
-      <c r="D51" t="n">
-        <v>498.3321</v>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-32.2156-498.3321</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>0.085</t>
         </is>
@@ -2879,13 +2824,12 @@
       <c r="B52" t="n">
         <v>-1.5809</v>
       </c>
-      <c r="C52" t="n">
-        <v>-3.6565</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.4947</v>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-3.6565-0.4947</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>0.135</t>
         </is>
@@ -2900,13 +2844,12 @@
       <c r="B53" t="n">
         <v>1.0205</v>
       </c>
-      <c r="C53" t="n">
-        <v>0.2475</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.7935</v>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0.2475-1.7935</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
@@ -2917,7 +2860,6 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55">
@@ -2927,7 +2869,6 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2942,7 +2883,6 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2957,7 +2897,6 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2972,7 +2911,6 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2987,7 +2925,6 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2998,7 +2935,6 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3009,13 +2945,12 @@
       <c r="B61" t="n">
         <v>322.5107</v>
       </c>
-      <c r="C61" t="n">
-        <v>176.0425</v>
-      </c>
-      <c r="D61" t="n">
-        <v>468.9789</v>
-      </c>
-      <c r="E61" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>176.0425-468.9789</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -3030,13 +2965,12 @@
       <c r="B62" t="n">
         <v>-0.9008</v>
       </c>
-      <c r="C62" t="n">
-        <v>-46.3087</v>
-      </c>
-      <c r="D62" t="n">
-        <v>44.5071</v>
-      </c>
-      <c r="E62" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-46.3087-44.5071</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>0.969</t>
         </is>
@@ -3051,13 +2985,12 @@
       <c r="B63" t="n">
         <v>56.4384</v>
       </c>
-      <c r="C63" t="n">
-        <v>-29.8154</v>
-      </c>
-      <c r="D63" t="n">
-        <v>142.6922</v>
-      </c>
-      <c r="E63" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-29.8154-142.6922</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>0.199</t>
         </is>
@@ -3072,13 +3005,12 @@
       <c r="B64" t="n">
         <v>-0.1854</v>
       </c>
-      <c r="C64" t="n">
-        <v>-2.3919</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2.0211</v>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-2.3919-2.0211</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>0.869</t>
         </is>
@@ -3093,13 +3025,12 @@
       <c r="B65" t="n">
         <v>0.5122</v>
       </c>
-      <c r="C65" t="n">
-        <v>-0.3236</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1.348</v>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-0.3236-1.348</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>0.229</t>
         </is>
@@ -3110,7 +3041,6 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3171,12 +3101,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.277</t>
+          <t>3.473</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.070</t>
+          <t>0.062</t>
         </is>
       </c>
     </row>

--- a/result/XRCC3_LUAD_Tables.xlsx
+++ b/result/XRCC3_LUAD_Tables.xlsx
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>415.6087</v>
+        <v>415.609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.2323</v>
+        <v>7.232</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.9199</v>
+        <v>-1.92</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.0564</v>
+        <v>1.056</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2280,11 +2280,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>409.3715</v>
+        <v>409.372</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>269.411-549.3321</t>
+          <t>269.411-549.332</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.7775</v>
+        <v>6.777</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-35.8426-49.3976</t>
+          <t>-35.843-49.398</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2320,11 +2320,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.5578</v>
+        <v>-1.558</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-52.7712-49.6556</t>
+          <t>-52.771-49.656</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2340,11 +2340,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2108</v>
+        <v>0.211</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-56.8703-57.2919</t>
+          <t>-56.87-57.292</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2360,11 +2360,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39.9474</v>
+        <v>39.947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-55.2119-135.1067</t>
+          <t>-55.212-135.107</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2380,11 +2380,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.8352</v>
+        <v>-1.835</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.9031-0.2326</t>
+          <t>-3.903-0.233</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.2765-1.8196</t>
+          <t>0.276-1.82</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2501,11 +2501,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>406.4946</v>
+        <v>406.495</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>267.9957-544.9935</t>
+          <t>267.996-544.994</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2521,11 +2521,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.9377</v>
+        <v>1.938</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-40.523-44.3985</t>
+          <t>-40.523-44.398</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2541,11 +2541,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.8701</v>
+        <v>31.87</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-13.4147-77.1549</t>
+          <t>-13.415-77.155</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2561,11 +2561,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-14.3775</v>
+        <v>-14.378</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-90.7573-62.0022</t>
+          <t>-90.757-62.002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2581,11 +2581,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-85.7345</v>
+        <v>-85.735</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-193.7031-22.234</t>
+          <t>-193.703-22.234</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2601,11 +2601,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.9792</v>
+        <v>-1.979</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-3.9999-0.0415</t>
+          <t>-4.0-0.042</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.3733-1.8947</t>
+          <t>0.373-1.895</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>256.8791-535.7149</t>
+          <t>256.879-535.715</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2742,11 +2742,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10.5203</v>
+        <v>10.52</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-32.025-53.0657</t>
+          <t>-32.025-53.066</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-16.4483</v>
+        <v>-16.448</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-70.1653-37.2687</t>
+          <t>-70.165-37.269</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2782,11 +2782,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6071</v>
+        <v>0.607</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-59.4938-60.708</t>
+          <t>-59.494-60.708</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2802,11 +2802,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>233.0582</v>
+        <v>233.058</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-32.2156-498.3321</t>
+          <t>-32.216-498.332</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2822,11 +2822,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.5809</v>
+        <v>-1.581</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-3.6565-0.4947</t>
+          <t>-3.656-0.495</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2842,11 +2842,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.0205</v>
+        <v>1.02</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.2475-1.7935</t>
+          <t>0.248-1.793</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2943,11 +2943,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>322.5107</v>
+        <v>322.511</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>176.0425-468.9789</t>
+          <t>176.042-468.979</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2963,11 +2963,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.9008</v>
+        <v>-0.901</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-46.3087-44.5071</t>
+          <t>-46.309-44.507</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2983,11 +2983,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>56.4384</v>
+        <v>56.438</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-29.8154-142.6922</t>
+          <t>-29.815-142.692</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3003,11 +3003,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.1854</v>
+        <v>-0.185</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>-2.3919-2.0211</t>
+          <t>-2.392-2.021</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3023,11 +3023,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5122</v>
+        <v>0.512</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-0.3236-1.348</t>
+          <t>-0.324-1.348</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">

--- a/result/XRCC3_LUAD_Tables.xlsx
+++ b/result/XRCC3_LUAD_Tables.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,27 +875,47 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PLAURexpression</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SNAI1expression</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>VEGFCexpression</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EGFRExpression</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -927,27 +947,47 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>-0.080</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.103</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.025</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>0.066</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>-0.073</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>-0.005</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>0.060</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.074</t>
         </is>
       </c>
     </row>
@@ -971,27 +1011,47 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.076</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.974</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.094</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.022</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.575</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>0.144</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0.107</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>0.905</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>0.185</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.281</t>
         </is>
       </c>
     </row>
@@ -1023,27 +1083,47 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.071</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.007</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>-0.016</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1067,27 +1147,47 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.198</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.906</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.837</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>0.774</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.611</t>
         </is>
       </c>
     </row>
@@ -1119,27 +1219,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0.060</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-0.068</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.086</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.027</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>-0.022</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0.072</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>-0.048</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>-0.050</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1163,34 +1283,54 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.182</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.130</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.057</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.551</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.983</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>0.624</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.112</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>0.291</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>0.265</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.865</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>ITGB1expression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1200,17 +1340,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1220,22 +1360,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.057</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.202</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-0.099</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-0.120</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-0.091</t>
         </is>
       </c>
     </row>
@@ -1248,45 +1408,65 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.043</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>PLAURexpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,42 +1476,62 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.073</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>-0.068</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0.323</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.341</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>-0.057</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.067</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.008</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>-0.045</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-0.044</t>
         </is>
       </c>
     </row>
@@ -1344,45 +1544,65 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.974</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.130</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.054</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.316</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.326</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>SNAI1expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,27 +1612,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.048</t>
+          <t>-0.086</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1422,12 +1642,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>0.233</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>0.025</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-0.128</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>-0.070</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.018</t>
         </is>
       </c>
     </row>
@@ -1440,45 +1680,65 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.906</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.587</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.501</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.692</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>VEGFCexpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1488,32 +1748,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.060</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>0.233</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1523,7 +1783,27 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.041</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-0.058</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-0.102</t>
         </is>
       </c>
     </row>
@@ -1536,45 +1816,65 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.551</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.369</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.452</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.024</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EGFR_Mut_Binary</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1584,42 +1884,62 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.074</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.202</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-0.123</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>-0.024</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.061</t>
         </is>
       </c>
     </row>
@@ -1632,40 +1952,604 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>0.575</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.587</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.369</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.595</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.177</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KrasExpression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.066</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.039</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.022</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.482</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.624</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.054</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.501</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.452</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0.934</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0.078</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TP53Expression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-0.073</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.072</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-0.099</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-0.128</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.058</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-0.123</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.107</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.408</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>0.139</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0.904</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.469</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.122</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.940</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ALKExpression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-0.005</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-0.048</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-0.120</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-0.045</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-0.070</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-0.024</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.905</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.291</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.316</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.595</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.934</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.372</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BRAFExpression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.060</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-0.091</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-0.044</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.102</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.061</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.185</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.774</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.265</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.043</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.326</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.177</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0.078</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.940</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>0.372</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1678,7 +2562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,15 +2578,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1717,13 +2596,12 @@
       <c r="B2" t="n">
         <v>1.014</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.033</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.995-1.033</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.145</t>
         </is>
@@ -1738,13 +2616,12 @@
       <c r="B3" t="n">
         <v>0.999</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.007</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.992-1.007</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.857</t>
         </is>
@@ -1759,13 +2636,12 @@
       <c r="B4" t="n">
         <v>0.627</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.429-0.915</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.016</t>
         </is>
@@ -1780,13 +2656,12 @@
       <c r="B5" t="n">
         <v>1.189</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.807-1.750</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.382</t>
         </is>
@@ -1801,13 +2676,12 @@
       <c r="B6" t="n">
         <v>2.117</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.336</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.353</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.336-3.353</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.001</t>
         </is>
@@ -1822,13 +2696,12 @@
       <c r="B7" t="n">
         <v>2.784</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.736</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.466</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.736-4.466</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1843,13 +2716,12 @@
       <c r="B8" t="n">
         <v>2.553</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.265</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5.152</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.265-5.152</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.009</t>
         </is>
@@ -1866,7 +2738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1882,15 +2754,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1905,13 +2772,12 @@
       <c r="B2" t="n">
         <v>1.014</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.033</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.996-1.033</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.135</t>
         </is>
@@ -1926,13 +2792,12 @@
       <c r="B3" t="n">
         <v>0.999</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.992-1.006</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.785</t>
         </is>
@@ -1947,13 +2812,12 @@
       <c r="B4" t="n">
         <v>1.483</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.246</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.764</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.246-1.764</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1968,13 +2832,12 @@
       <c r="B5" t="n">
         <v>0.635</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.435-0.927</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.019</t>
         </is>
@@ -1989,13 +2852,12 @@
       <c r="B6" t="n">
         <v>1.21</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.828</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.828-1.770</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.325</t>
         </is>
@@ -3101,12 +3963,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.473</t>
+          <t>7.952</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.047</t>
         </is>
       </c>
     </row>
@@ -3128,12 +3990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.657</t>
+          <t>6.372</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.095</t>
         </is>
       </c>
     </row>
